--- a/data/k-props/2026-08-20.xlsx
+++ b/data/k-props/2026-08-20.xlsx
@@ -133,87 +133,87 @@
     <t>08/20/2026</t>
   </si>
   <si>
+    <t>Michael McGreevy</t>
+  </si>
+  <si>
+    <t>St. Louis Cardinals @ Cincinnati Reds</t>
+  </si>
+  <si>
+    <t>Traditional starter</t>
+  </si>
+  <si>
+    <t>lineup_unweighted_30d_posted</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>&lt;6</t>
+  </si>
+  <si>
     <t>Brady Singer</t>
   </si>
   <si>
-    <t>St. Louis Cardinals @ Cincinnati Reds</t>
-  </si>
-  <si>
-    <t>Traditional starter</t>
-  </si>
-  <si>
-    <t>lineup_unweighted_30d_posted</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>&lt;6</t>
-  </si>
-  <si>
-    <t>Michael McGreevy</t>
+    <t>Landen Roupp</t>
+  </si>
+  <si>
+    <t>San Francisco Giants @ Cleveland Guardians</t>
   </si>
   <si>
     <t>Gavin Williams</t>
   </si>
   <si>
-    <t>San Francisco Giants @ Cleveland Guardians</t>
-  </si>
-  <si>
     <t>&gt;=7</t>
   </si>
   <si>
-    <t>Landen Roupp</t>
+    <t>Shane Bieber</t>
+  </si>
+  <si>
+    <t>Toronto Blue Jays @ Tampa Bay Rays</t>
   </si>
   <si>
     <t>Ian Seymour</t>
   </si>
   <si>
-    <t>Toronto Blue Jays @ Tampa Bay Rays</t>
-  </si>
-  <si>
-    <t>Shane Bieber</t>
+    <t>Gage Jump</t>
+  </si>
+  <si>
+    <t>Athletics @ Kansas City Royals</t>
+  </si>
+  <si>
+    <t>Randy Dobnak</t>
+  </si>
+  <si>
+    <t>Grant Holmes</t>
+  </si>
+  <si>
+    <t>Atlanta Braves @ Chicago White Sox</t>
   </si>
   <si>
     <t>Anthony Kay</t>
   </si>
   <si>
-    <t>Atlanta Braves @ Chicago White Sox</t>
-  </si>
-  <si>
-    <t>Grant Holmes</t>
-  </si>
-  <si>
-    <t>Gage Jump</t>
-  </si>
-  <si>
-    <t>Athletics @ Kansas City Royals</t>
-  </si>
-  <si>
-    <t>Randy Dobnak</t>
+    <t>George Kirby</t>
+  </si>
+  <si>
+    <t>Seattle Mariners @ Milwaukee Brewers</t>
+  </si>
+  <si>
+    <t>Robert Gasser</t>
+  </si>
+  <si>
+    <t>Gerrit Cole</t>
+  </si>
+  <si>
+    <t>New York Yankees @ Baltimore Orioles</t>
   </si>
   <si>
     <t>lineup_unweighted_30d_projected_regulars</t>
   </si>
   <si>
-    <t>George Kirby</t>
-  </si>
-  <si>
-    <t>Seattle Mariners @ Milwaukee Brewers</t>
-  </si>
-  <si>
-    <t>Robert Gasser</t>
-  </si>
-  <si>
     <t>Kyle Bradish</t>
   </si>
   <si>
-    <t>New York Yankees @ Baltimore Orioles</t>
-  </si>
-  <si>
-    <t>Gerrit Cole</t>
-  </si>
-  <si>
     <t>Andrew Alvarez</t>
   </si>
   <si>
@@ -223,16 +223,16 @@
     <t>Jacob deGrom</t>
   </si>
   <si>
+    <t>Grayson Rodriguez</t>
+  </si>
+  <si>
+    <t>Los Angeles Angels @ Houston Astros</t>
+  </si>
+  <si>
     <t>Peter Lambert</t>
   </si>
   <si>
-    <t>Los Angeles Angels @ Houston Astros</t>
-  </si>
-  <si>
     <t>6-7</t>
-  </si>
-  <si>
-    <t>Grayson Rodriguez</t>
   </si>
 </sst>
 </file>
@@ -749,10 +749,10 @@
         <v>4.5</v>
       </c>
       <c r="D2">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="E2">
-        <v>-130</v>
+        <v>-120</v>
       </c>
       <c r="F2" t="s">
         <v>41</v>
@@ -764,7 +764,7 @@
         <v>42</v>
       </c>
       <c r="I2">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="J2" t="b">
         <v>0</v>
@@ -776,43 +776,43 @@
         <v>6</v>
       </c>
       <c r="M2">
-        <v>0.1867</v>
+        <v>0.1691</v>
       </c>
       <c r="N2">
         <v>5</v>
       </c>
       <c r="O2">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="P2">
-        <v>4.43</v>
+        <v>4.08</v>
       </c>
       <c r="Q2">
-        <v>0.1705</v>
+        <v>0.1802</v>
       </c>
       <c r="R2">
-        <v>0.392</v>
+        <v>0.357</v>
       </c>
       <c r="S2" t="s">
         <v>43</v>
       </c>
       <c r="T2">
-        <v>0.2156</v>
+        <v>0.2892</v>
       </c>
       <c r="U2">
-        <v>0.2069</v>
+        <v>0.2778</v>
       </c>
       <c r="V2">
         <v>9</v>
       </c>
       <c r="W2">
-        <v>0.2143</v>
+        <v>0.2559</v>
       </c>
       <c r="X2">
-        <v>0.2248</v>
+        <v>0.2216</v>
       </c>
       <c r="Y2">
-        <v>1.017</v>
+        <v>1.0392</v>
       </c>
       <c r="AA2" t="s">
         <v>44</v>
@@ -821,22 +821,22 @@
         <v>44</v>
       </c>
       <c r="AD2">
-        <v>4.08</v>
+        <v>5.26</v>
       </c>
       <c r="AE2" t="s">
         <v>45</v>
       </c>
       <c r="AF2">
-        <v>0.1804</v>
+        <v>0.1731</v>
       </c>
       <c r="AG2">
-        <v>0.9591</v>
+        <v>1.3047</v>
       </c>
       <c r="AH2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>4.08</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
@@ -850,10 +850,10 @@
         <v>4.5</v>
       </c>
       <c r="D3">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="E3">
-        <v>-120</v>
+        <v>-130</v>
       </c>
       <c r="F3" t="s">
         <v>41</v>
@@ -865,7 +865,7 @@
         <v>42</v>
       </c>
       <c r="I3">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="J3" t="b">
         <v>0</v>
@@ -877,43 +877,43 @@
         <v>6</v>
       </c>
       <c r="M3">
-        <v>0.1691</v>
+        <v>0.1864</v>
       </c>
       <c r="N3">
         <v>5</v>
       </c>
       <c r="O3">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="P3">
-        <v>4.08</v>
+        <v>4.44</v>
       </c>
       <c r="Q3">
-        <v>0.1802</v>
+        <v>0.1705</v>
       </c>
       <c r="R3">
-        <v>0.357</v>
+        <v>0.392</v>
       </c>
       <c r="S3" t="s">
         <v>43</v>
       </c>
       <c r="T3">
-        <v>0.2892</v>
+        <v>0.2156</v>
       </c>
       <c r="U3">
-        <v>0.2778</v>
+        <v>0.2069</v>
       </c>
       <c r="V3">
         <v>9</v>
       </c>
       <c r="W3">
-        <v>0.2559</v>
+        <v>0.2143</v>
       </c>
       <c r="X3">
-        <v>0.2248</v>
+        <v>0.2216</v>
       </c>
       <c r="Y3">
-        <v>1.0392</v>
+        <v>1.017</v>
       </c>
       <c r="AA3" t="s">
         <v>44</v>
@@ -922,22 +922,22 @@
         <v>44</v>
       </c>
       <c r="AD3">
-        <v>5.19</v>
+        <v>3.98</v>
       </c>
       <c r="AE3" t="s">
         <v>45</v>
       </c>
       <c r="AF3">
-        <v>0.1731</v>
+        <v>0.1802</v>
       </c>
       <c r="AG3">
-        <v>1.2861</v>
+        <v>0.973</v>
       </c>
       <c r="AH3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>5.19</v>
+        <v>3.98</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -948,13 +948,13 @@
         <v>47</v>
       </c>
       <c r="C4">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="D4">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="E4">
-        <v>-114</v>
+        <v>-139</v>
       </c>
       <c r="F4" t="s">
         <v>48</v>
@@ -966,55 +966,55 @@
         <v>42</v>
       </c>
       <c r="I4">
+        <v>5.4</v>
+      </c>
+      <c r="J4" t="b">
+        <v>0</v>
+      </c>
+      <c r="K4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4">
         <v>6</v>
       </c>
-      <c r="J4" t="b">
-        <v>0</v>
-      </c>
-      <c r="K4" t="b">
-        <v>0</v>
-      </c>
-      <c r="L4">
-        <v>5</v>
-      </c>
       <c r="M4">
-        <v>0.3183</v>
+        <v>0.2336</v>
       </c>
       <c r="N4">
         <v>5</v>
       </c>
       <c r="O4">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P4">
-        <v>4.01</v>
+        <v>4.24</v>
       </c>
       <c r="Q4">
-        <v>0.4018</v>
+        <v>0.1947</v>
       </c>
       <c r="R4">
-        <v>0.359</v>
+        <v>0.361</v>
       </c>
       <c r="S4" t="s">
         <v>43</v>
       </c>
       <c r="T4">
-        <v>0.2087</v>
+        <v>0.1552</v>
       </c>
       <c r="U4">
-        <v>0.2085</v>
+        <v>0.1566</v>
       </c>
       <c r="V4">
         <v>9</v>
       </c>
       <c r="W4">
-        <v>0.2027</v>
+        <v>0.2157</v>
       </c>
       <c r="X4">
-        <v>0.2248</v>
+        <v>0.2216</v>
       </c>
       <c r="Y4">
-        <v>0.9792</v>
+        <v>0.8801</v>
       </c>
       <c r="AA4" t="s">
         <v>44</v>
@@ -1023,22 +1023,22 @@
         <v>44</v>
       </c>
       <c r="AD4">
-        <v>7.56</v>
+        <v>3.09</v>
       </c>
       <c r="AE4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="AF4">
-        <v>0.3482</v>
+        <v>0.2195</v>
       </c>
       <c r="AG4">
-        <v>0.9281</v>
+        <v>0.7004</v>
       </c>
       <c r="AH4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>7.56</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
@@ -1046,16 +1046,16 @@
         <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C5">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="D5">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="E5">
-        <v>-139</v>
+        <v>-114</v>
       </c>
       <c r="F5" t="s">
         <v>48</v>
@@ -1067,7 +1067,7 @@
         <v>42</v>
       </c>
       <c r="I5">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
@@ -1076,46 +1076,46 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M5">
-        <v>0.2336</v>
+        <v>0.3183</v>
       </c>
       <c r="N5">
         <v>5</v>
       </c>
       <c r="O5">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P5">
-        <v>4.24</v>
+        <v>4.01</v>
       </c>
       <c r="Q5">
-        <v>0.1947</v>
+        <v>0.4018</v>
       </c>
       <c r="R5">
-        <v>0.361</v>
+        <v>0.359</v>
       </c>
       <c r="S5" t="s">
         <v>43</v>
       </c>
       <c r="T5">
-        <v>0.1552</v>
+        <v>0.2087</v>
       </c>
       <c r="U5">
-        <v>0.1566</v>
+        <v>0.2085</v>
       </c>
       <c r="V5">
         <v>9</v>
       </c>
       <c r="W5">
-        <v>0.2157</v>
+        <v>0.2027</v>
       </c>
       <c r="X5">
-        <v>0.2248</v>
+        <v>0.2216</v>
       </c>
       <c r="Y5">
-        <v>0.8801</v>
+        <v>0.9792</v>
       </c>
       <c r="AA5" t="s">
         <v>44</v>
@@ -1124,22 +1124,22 @@
         <v>44</v>
       </c>
       <c r="AD5">
-        <v>3.05</v>
+        <v>7.67</v>
       </c>
       <c r="AE5" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="AF5">
-        <v>0.2195</v>
+        <v>0.3482</v>
       </c>
       <c r="AG5">
-        <v>0.6904</v>
+        <v>0.9415</v>
       </c>
       <c r="AH5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>3.05</v>
+        <v>7.67</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1150,13 +1150,13 @@
         <v>51</v>
       </c>
       <c r="C6">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="D6">
-        <v>120</v>
+        <v>-122</v>
       </c>
       <c r="E6">
-        <v>-134</v>
+        <v>110</v>
       </c>
       <c r="F6" t="s">
         <v>52</v>
@@ -1168,7 +1168,7 @@
         <v>42</v>
       </c>
       <c r="I6">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
@@ -1180,43 +1180,43 @@
         <v>6</v>
       </c>
       <c r="M6">
-        <v>0.2882</v>
+        <v>0.1705</v>
       </c>
       <c r="N6">
         <v>5</v>
       </c>
       <c r="O6">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P6">
-        <v>4.14</v>
+        <v>4.46</v>
       </c>
       <c r="Q6">
-        <v>0.2963</v>
+        <v>0.1651</v>
       </c>
       <c r="R6">
-        <v>0.351</v>
+        <v>0.353</v>
       </c>
       <c r="S6" t="s">
         <v>43</v>
       </c>
       <c r="T6">
-        <v>0.1695</v>
+        <v>0.1603</v>
       </c>
       <c r="U6">
-        <v>0.1658</v>
+        <v>0.1697</v>
       </c>
       <c r="V6">
         <v>9</v>
       </c>
       <c r="W6">
-        <v>0.2075</v>
+        <v>0.1876</v>
       </c>
       <c r="X6">
-        <v>0.2248</v>
+        <v>0.2216</v>
       </c>
       <c r="Y6">
-        <v>0.9434</v>
+        <v>0.88</v>
       </c>
       <c r="AA6" t="s">
         <v>44</v>
@@ -1225,22 +1225,22 @@
         <v>44</v>
       </c>
       <c r="AD6">
-        <v>4</v>
+        <v>2.33</v>
       </c>
       <c r="AE6" t="s">
         <v>45</v>
       </c>
       <c r="AF6">
-        <v>0.2911</v>
+        <v>0.1686</v>
       </c>
       <c r="AG6">
-        <v>0.7539</v>
+        <v>0.7231</v>
       </c>
       <c r="AH6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>4</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
@@ -1251,13 +1251,13 @@
         <v>53</v>
       </c>
       <c r="C7">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="D7">
-        <v>-122</v>
+        <v>120</v>
       </c>
       <c r="E7">
-        <v>110</v>
+        <v>-134</v>
       </c>
       <c r="F7" t="s">
         <v>52</v>
@@ -1269,7 +1269,7 @@
         <v>42</v>
       </c>
       <c r="I7">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
@@ -1281,43 +1281,43 @@
         <v>6</v>
       </c>
       <c r="M7">
-        <v>0.1705</v>
+        <v>0.2882</v>
       </c>
       <c r="N7">
         <v>5</v>
       </c>
       <c r="O7">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P7">
-        <v>4.46</v>
+        <v>4.14</v>
       </c>
       <c r="Q7">
-        <v>0.1651</v>
+        <v>0.2963</v>
       </c>
       <c r="R7">
-        <v>0.353</v>
+        <v>0.351</v>
       </c>
       <c r="S7" t="s">
         <v>43</v>
       </c>
       <c r="T7">
-        <v>0.1603</v>
+        <v>0.1695</v>
       </c>
       <c r="U7">
-        <v>0.1697</v>
+        <v>0.1658</v>
       </c>
       <c r="V7">
         <v>9</v>
       </c>
       <c r="W7">
-        <v>0.1876</v>
+        <v>0.2075</v>
       </c>
       <c r="X7">
-        <v>0.2248</v>
+        <v>0.2216</v>
       </c>
       <c r="Y7">
-        <v>0.88</v>
+        <v>0.9434</v>
       </c>
       <c r="AA7" t="s">
         <v>44</v>
@@ -1326,22 +1326,22 @@
         <v>44</v>
       </c>
       <c r="AD7">
-        <v>2.29</v>
+        <v>4.06</v>
       </c>
       <c r="AE7" t="s">
         <v>45</v>
       </c>
       <c r="AF7">
-        <v>0.1686</v>
+        <v>0.2911</v>
       </c>
       <c r="AG7">
-        <v>0.7128</v>
+        <v>0.7648</v>
       </c>
       <c r="AH7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>2.29</v>
+        <v>4.06</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
@@ -1355,22 +1355,22 @@
         <v>4.5</v>
       </c>
       <c r="D8">
-        <v>120</v>
+        <v>-141</v>
       </c>
       <c r="E8">
-        <v>-130</v>
+        <v>116</v>
       </c>
       <c r="F8" t="s">
         <v>55</v>
       </c>
       <c r="G8">
-        <v>824589</v>
+        <v>824074</v>
       </c>
       <c r="H8" t="s">
         <v>42</v>
       </c>
       <c r="I8">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
@@ -1382,43 +1382,43 @@
         <v>6</v>
       </c>
       <c r="M8">
-        <v>0.1811</v>
+        <v>0.2515</v>
       </c>
       <c r="N8">
         <v>5</v>
       </c>
       <c r="O8">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="P8">
-        <v>4.46</v>
+        <v>4.33</v>
       </c>
       <c r="Q8">
-        <v>0.1849</v>
+        <v>0.2479</v>
       </c>
       <c r="R8">
-        <v>0.373</v>
+        <v>0.369</v>
       </c>
       <c r="S8" t="s">
         <v>43</v>
       </c>
       <c r="T8">
-        <v>0.2575</v>
+        <v>0.2053</v>
       </c>
       <c r="U8">
-        <v>0.2358</v>
+        <v>0.1871</v>
       </c>
       <c r="V8">
         <v>9</v>
       </c>
       <c r="W8">
-        <v>0.2079</v>
+        <v>0.2127</v>
       </c>
       <c r="X8">
-        <v>0.2248</v>
+        <v>0.2216</v>
       </c>
       <c r="Y8">
-        <v>0.9771</v>
+        <v>0.88</v>
       </c>
       <c r="AA8" t="s">
         <v>44</v>
@@ -1427,22 +1427,22 @@
         <v>44</v>
       </c>
       <c r="AD8">
-        <v>4.53</v>
+        <v>4.59</v>
       </c>
       <c r="AE8" t="s">
         <v>45</v>
       </c>
       <c r="AF8">
-        <v>0.1825</v>
+        <v>0.2501</v>
       </c>
       <c r="AG8">
-        <v>1.1453</v>
+        <v>0.9263</v>
       </c>
       <c r="AH8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>4.53</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1453,25 +1453,25 @@
         <v>56</v>
       </c>
       <c r="C9">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D9">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E9">
-        <v>-135</v>
+        <v>-149</v>
       </c>
       <c r="F9" t="s">
         <v>55</v>
       </c>
       <c r="G9">
-        <v>824589</v>
+        <v>824074</v>
       </c>
       <c r="H9" t="s">
         <v>42</v>
       </c>
       <c r="I9">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
@@ -1483,43 +1483,43 @@
         <v>6</v>
       </c>
       <c r="M9">
-        <v>0.1913</v>
+        <v>0.142</v>
       </c>
       <c r="N9">
         <v>5</v>
       </c>
       <c r="O9">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="P9">
-        <v>4.31</v>
+        <v>4.22</v>
       </c>
       <c r="Q9">
-        <v>0.1776</v>
+        <v>0.1579</v>
       </c>
       <c r="R9">
-        <v>0.349</v>
+        <v>0.363</v>
       </c>
       <c r="S9" t="s">
         <v>43</v>
       </c>
       <c r="T9">
-        <v>0.2355</v>
+        <v>0.2019</v>
       </c>
       <c r="U9">
-        <v>0.2393</v>
+        <v>0.2012</v>
       </c>
       <c r="V9">
         <v>9</v>
       </c>
       <c r="W9">
-        <v>0.2352</v>
+        <v>0.2126</v>
       </c>
       <c r="X9">
-        <v>0.2248</v>
+        <v>0.2216</v>
       </c>
       <c r="Y9">
-        <v>1.0597</v>
+        <v>1.0024</v>
       </c>
       <c r="AA9" t="s">
         <v>44</v>
@@ -1528,22 +1528,22 @@
         <v>44</v>
       </c>
       <c r="AD9">
-        <v>4.41</v>
+        <v>3.04</v>
       </c>
       <c r="AE9" t="s">
         <v>45</v>
       </c>
       <c r="AF9">
-        <v>0.1865</v>
+        <v>0.1478</v>
       </c>
       <c r="AG9">
-        <v>1.0475</v>
+        <v>0.911</v>
       </c>
       <c r="AH9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>4.41</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
@@ -1557,22 +1557,22 @@
         <v>4.5</v>
       </c>
       <c r="D10">
-        <v>-141</v>
+        <v>123</v>
       </c>
       <c r="E10">
-        <v>116</v>
+        <v>-135</v>
       </c>
       <c r="F10" t="s">
         <v>58</v>
       </c>
       <c r="G10">
-        <v>824074</v>
+        <v>824589</v>
       </c>
       <c r="H10" t="s">
         <v>42</v>
       </c>
       <c r="I10">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
@@ -1584,43 +1584,43 @@
         <v>6</v>
       </c>
       <c r="M10">
-        <v>0.2515</v>
+        <v>0.1913</v>
       </c>
       <c r="N10">
         <v>5</v>
       </c>
       <c r="O10">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="P10">
-        <v>4.33</v>
+        <v>4.31</v>
       </c>
       <c r="Q10">
-        <v>0.2479</v>
+        <v>0.1776</v>
       </c>
       <c r="R10">
-        <v>0.369</v>
+        <v>0.349</v>
       </c>
       <c r="S10" t="s">
         <v>43</v>
       </c>
       <c r="T10">
-        <v>0.2053</v>
+        <v>0.2355</v>
       </c>
       <c r="U10">
-        <v>0.1871</v>
+        <v>0.2393</v>
       </c>
       <c r="V10">
         <v>9</v>
       </c>
       <c r="W10">
-        <v>0.2127</v>
+        <v>0.2352</v>
       </c>
       <c r="X10">
-        <v>0.2248</v>
+        <v>0.2216</v>
       </c>
       <c r="Y10">
-        <v>0.88</v>
+        <v>1.0597</v>
       </c>
       <c r="AA10" t="s">
         <v>44</v>
@@ -1629,22 +1629,22 @@
         <v>44</v>
       </c>
       <c r="AD10">
-        <v>4.53</v>
+        <v>4.47</v>
       </c>
       <c r="AE10" t="s">
         <v>45</v>
       </c>
       <c r="AF10">
-        <v>0.2501</v>
+        <v>0.1865</v>
       </c>
       <c r="AG10">
-        <v>0.913</v>
+        <v>1.0627</v>
       </c>
       <c r="AH10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>4.53</v>
+        <v>4.47</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -1655,25 +1655,25 @@
         <v>59</v>
       </c>
       <c r="C11">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D11">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E11">
-        <v>-149</v>
+        <v>-130</v>
       </c>
       <c r="F11" t="s">
         <v>58</v>
       </c>
       <c r="G11">
-        <v>824074</v>
+        <v>824589</v>
       </c>
       <c r="H11" t="s">
         <v>42</v>
       </c>
       <c r="I11">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="J11" t="b">
         <v>0</v>
@@ -1685,43 +1685,43 @@
         <v>6</v>
       </c>
       <c r="M11">
-        <v>0.142</v>
+        <v>0.1811</v>
       </c>
       <c r="N11">
         <v>5</v>
       </c>
       <c r="O11">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="P11">
-        <v>4.22</v>
+        <v>4.46</v>
       </c>
       <c r="Q11">
-        <v>0.1579</v>
+        <v>0.1849</v>
       </c>
       <c r="R11">
-        <v>0.363</v>
+        <v>0.373</v>
       </c>
       <c r="S11" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="T11">
-        <v>0.2547</v>
+        <v>0.2575</v>
       </c>
       <c r="U11">
-        <v>0.2199</v>
+        <v>0.2358</v>
       </c>
       <c r="V11">
         <v>9</v>
       </c>
       <c r="W11">
-        <v>0.2126</v>
+        <v>0.2079</v>
       </c>
       <c r="X11">
-        <v>0.2248</v>
+        <v>0.2216</v>
       </c>
       <c r="Y11">
-        <v>1.0143</v>
+        <v>0.9771</v>
       </c>
       <c r="AA11" t="s">
         <v>44</v>
@@ -1730,22 +1730,22 @@
         <v>44</v>
       </c>
       <c r="AD11">
-        <v>3.83</v>
+        <v>4.59</v>
       </c>
       <c r="AE11" t="s">
         <v>45</v>
       </c>
       <c r="AF11">
-        <v>0.1478</v>
+        <v>0.1825</v>
       </c>
       <c r="AG11">
-        <v>1.1327</v>
+        <v>1.1619</v>
       </c>
       <c r="AH11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>3.83</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
@@ -1753,7 +1753,7 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C12">
         <v>4.5</v>
@@ -1765,7 +1765,7 @@
         <v>112</v>
       </c>
       <c r="F12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G12">
         <v>823747</v>
@@ -1804,25 +1804,25 @@
         <v>0.357</v>
       </c>
       <c r="S12" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="T12">
-        <v>0.2243</v>
+        <v>0.2407</v>
       </c>
       <c r="U12">
-        <v>0.2235</v>
+        <v>0.2358</v>
       </c>
       <c r="V12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W12">
         <v>0.2143</v>
       </c>
       <c r="X12">
-        <v>0.2248</v>
+        <v>0.2216</v>
       </c>
       <c r="Y12">
-        <v>0.9867</v>
+        <v>1.0224</v>
       </c>
       <c r="AA12" t="s">
         <v>44</v>
@@ -1831,7 +1831,7 @@
         <v>44</v>
       </c>
       <c r="AD12">
-        <v>4.39</v>
+        <v>4.95</v>
       </c>
       <c r="AE12" t="s">
         <v>45</v>
@@ -1840,13 +1840,13 @@
         <v>0.1807</v>
       </c>
       <c r="AG12">
-        <v>0.9978</v>
+        <v>1.0861</v>
       </c>
       <c r="AH12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>4.39</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
@@ -1854,7 +1854,7 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C13">
         <v>5.5</v>
@@ -1866,7 +1866,7 @@
         <v>-144</v>
       </c>
       <c r="F13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G13">
         <v>823747</v>
@@ -1905,13 +1905,13 @@
         <v>0.361</v>
       </c>
       <c r="S13" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="T13">
-        <v>0.2305</v>
+        <v>0.2091</v>
       </c>
       <c r="U13">
-        <v>0.2055</v>
+        <v>0.1862</v>
       </c>
       <c r="V13">
         <v>9</v>
@@ -1920,10 +1920,10 @@
         <v>0.2416</v>
       </c>
       <c r="X13">
-        <v>0.2248</v>
+        <v>0.2216</v>
       </c>
       <c r="Y13">
-        <v>0.9886</v>
+        <v>0.9308</v>
       </c>
       <c r="AA13" t="s">
         <v>44</v>
@@ -1932,7 +1932,7 @@
         <v>44</v>
       </c>
       <c r="AD13">
-        <v>4.96</v>
+        <v>4.3</v>
       </c>
       <c r="AE13" t="s">
         <v>45</v>
@@ -1941,13 +1941,13 @@
         <v>0.2182</v>
       </c>
       <c r="AG13">
-        <v>1.0252</v>
+        <v>0.9437</v>
       </c>
       <c r="AH13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>4.96</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -1955,19 +1955,19 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
+        <v>63</v>
+      </c>
+      <c r="C14">
+        <v>6.5</v>
+      </c>
+      <c r="D14">
+        <v>-122</v>
+      </c>
+      <c r="E14">
+        <v>-102</v>
+      </c>
+      <c r="F14" t="s">
         <v>64</v>
-      </c>
-      <c r="C14">
-        <v>5.5</v>
-      </c>
-      <c r="D14">
-        <v>-138</v>
-      </c>
-      <c r="E14">
-        <v>112</v>
-      </c>
-      <c r="F14" t="s">
-        <v>65</v>
       </c>
       <c r="G14">
         <v>824802</v>
@@ -1976,7 +1976,7 @@
         <v>42</v>
       </c>
       <c r="I14">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="J14" t="b">
         <v>0</v>
@@ -1988,43 +1988,43 @@
         <v>5</v>
       </c>
       <c r="M14">
-        <v>0.2206</v>
+        <v>0.2606</v>
       </c>
       <c r="N14">
         <v>5</v>
       </c>
       <c r="O14">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="P14">
-        <v>4.23</v>
+        <v>4.07</v>
       </c>
       <c r="Q14">
-        <v>0.1667</v>
+        <v>0.3008</v>
       </c>
       <c r="R14">
-        <v>0.351</v>
+        <v>0.381</v>
       </c>
       <c r="S14" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="T14">
-        <v>0.2724</v>
+        <v>0.252</v>
       </c>
       <c r="U14">
-        <v>0.2721</v>
+        <v>0.2407</v>
       </c>
       <c r="V14">
         <v>9</v>
       </c>
       <c r="W14">
-        <v>0.2465</v>
+        <v>0.2375</v>
       </c>
       <c r="X14">
-        <v>0.2248</v>
+        <v>0.2216</v>
       </c>
       <c r="Y14">
-        <v>1.0137</v>
+        <v>1.0328</v>
       </c>
       <c r="AA14" t="s">
         <v>44</v>
@@ -2033,22 +2033,22 @@
         <v>44</v>
       </c>
       <c r="AD14">
-        <v>5.8</v>
+        <v>7.63</v>
       </c>
       <c r="AE14" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="AF14">
-        <v>0.2017</v>
+        <v>0.2759</v>
       </c>
       <c r="AG14">
-        <v>1.2116</v>
+        <v>1.1372</v>
       </c>
       <c r="AH14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>5.8</v>
+        <v>7.63</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -2059,16 +2059,16 @@
         <v>66</v>
       </c>
       <c r="C15">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="D15">
-        <v>-122</v>
+        <v>-138</v>
       </c>
       <c r="E15">
-        <v>-102</v>
+        <v>112</v>
       </c>
       <c r="F15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G15">
         <v>824802</v>
@@ -2077,7 +2077,7 @@
         <v>42</v>
       </c>
       <c r="I15">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="J15" t="b">
         <v>0</v>
@@ -2089,43 +2089,43 @@
         <v>5</v>
       </c>
       <c r="M15">
-        <v>0.2606</v>
+        <v>0.2206</v>
       </c>
       <c r="N15">
         <v>5</v>
       </c>
       <c r="O15">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="P15">
-        <v>4.07</v>
+        <v>4.23</v>
       </c>
       <c r="Q15">
-        <v>0.3008</v>
+        <v>0.1667</v>
       </c>
       <c r="R15">
-        <v>0.381</v>
+        <v>0.351</v>
       </c>
       <c r="S15" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="T15">
-        <v>0.252</v>
+        <v>0.2724</v>
       </c>
       <c r="U15">
-        <v>0.2407</v>
+        <v>0.2721</v>
       </c>
       <c r="V15">
         <v>9</v>
       </c>
       <c r="W15">
-        <v>0.2375</v>
+        <v>0.2465</v>
       </c>
       <c r="X15">
-        <v>0.2248</v>
+        <v>0.2216</v>
       </c>
       <c r="Y15">
-        <v>1.0328</v>
+        <v>1.0137</v>
       </c>
       <c r="AA15" t="s">
         <v>44</v>
@@ -2134,22 +2134,22 @@
         <v>44</v>
       </c>
       <c r="AD15">
-        <v>7.52</v>
+        <v>5.89</v>
       </c>
       <c r="AE15" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="AF15">
-        <v>0.2759</v>
+        <v>0.2017</v>
       </c>
       <c r="AG15">
-        <v>1.1209</v>
+        <v>1.2292</v>
       </c>
       <c r="AH15">
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>7.52</v>
+        <v>5.89</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -2208,7 +2208,7 @@
         <v>0.361</v>
       </c>
       <c r="S16" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="T16">
         <v>0.2349</v>
@@ -2223,7 +2223,7 @@
         <v>0.2467</v>
       </c>
       <c r="X16">
-        <v>0.2248</v>
+        <v>0.2216</v>
       </c>
       <c r="Y16">
         <v>1.0156</v>
@@ -2235,7 +2235,7 @@
         <v>44</v>
       </c>
       <c r="AD16">
-        <v>4.12</v>
+        <v>4.18</v>
       </c>
       <c r="AE16" t="s">
         <v>45</v>
@@ -2244,13 +2244,13 @@
         <v>0.1902</v>
       </c>
       <c r="AG16">
-        <v>1.0446</v>
+        <v>1.0597</v>
       </c>
       <c r="AH16">
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>4.12</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
@@ -2309,7 +2309,7 @@
         <v>0.327</v>
       </c>
       <c r="S17" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="T17">
         <v>0.2027</v>
@@ -2324,7 +2324,7 @@
         <v>0.2066</v>
       </c>
       <c r="X17">
-        <v>0.2248</v>
+        <v>0.2216</v>
       </c>
       <c r="Y17">
         <v>1.0123</v>
@@ -2336,7 +2336,7 @@
         <v>44</v>
       </c>
       <c r="AD17">
-        <v>5.59</v>
+        <v>5.67</v>
       </c>
       <c r="AE17" t="s">
         <v>45</v>
@@ -2345,13 +2345,13 @@
         <v>0.2829</v>
       </c>
       <c r="AG17">
-        <v>0.9014</v>
+        <v>0.9145</v>
       </c>
       <c r="AH17">
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>5.59</v>
+        <v>5.67</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
@@ -2362,13 +2362,13 @@
         <v>70</v>
       </c>
       <c r="C18">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D18">
-        <v>-106</v>
+        <v>-113</v>
       </c>
       <c r="E18">
-        <v>-114</v>
+        <v>104</v>
       </c>
       <c r="F18" t="s">
         <v>71</v>
@@ -2380,7 +2380,7 @@
         <v>42</v>
       </c>
       <c r="I18">
-        <v>5.7</v>
+        <v>4.5</v>
       </c>
       <c r="J18" t="b">
         <v>0</v>
@@ -2392,43 +2392,43 @@
         <v>6</v>
       </c>
       <c r="M18">
-        <v>0.2368</v>
+        <v>0.203</v>
       </c>
       <c r="N18">
         <v>5</v>
       </c>
       <c r="O18">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="P18">
-        <v>4.16</v>
+        <v>4.59</v>
       </c>
       <c r="Q18">
-        <v>0.2261</v>
+        <v>0.2718</v>
       </c>
       <c r="R18">
-        <v>0.365</v>
+        <v>0.34</v>
       </c>
       <c r="S18" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="T18">
-        <v>0.2676</v>
+        <v>0.2112</v>
       </c>
       <c r="U18">
-        <v>0.255</v>
+        <v>0.2024</v>
       </c>
       <c r="V18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W18">
-        <v>0.2507</v>
+        <v>0.2184</v>
       </c>
       <c r="X18">
-        <v>0.2248</v>
+        <v>0.2216</v>
       </c>
       <c r="Y18">
-        <v>1.0315</v>
+        <v>0.9863</v>
       </c>
       <c r="AA18" t="s">
         <v>44</v>
@@ -2437,22 +2437,22 @@
         <v>44</v>
       </c>
       <c r="AD18">
-        <v>6.73</v>
+        <v>4.43</v>
       </c>
       <c r="AE18" t="s">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="AF18">
-        <v>0.2329</v>
+        <v>0.2264</v>
       </c>
       <c r="AG18">
-        <v>1.1902</v>
+        <v>0.9527</v>
       </c>
       <c r="AH18">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="AM18">
-        <v>6.91</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -2460,16 +2460,16 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C19">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D19">
-        <v>-113</v>
+        <v>-106</v>
       </c>
       <c r="E19">
-        <v>104</v>
+        <v>-114</v>
       </c>
       <c r="F19" t="s">
         <v>71</v>
@@ -2481,7 +2481,7 @@
         <v>42</v>
       </c>
       <c r="I19">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="J19" t="b">
         <v>0</v>
@@ -2493,43 +2493,43 @@
         <v>6</v>
       </c>
       <c r="M19">
-        <v>0.203</v>
+        <v>0.2368</v>
       </c>
       <c r="N19">
         <v>5</v>
       </c>
       <c r="O19">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="P19">
-        <v>4.59</v>
+        <v>4.16</v>
       </c>
       <c r="Q19">
-        <v>0.2718</v>
+        <v>0.2261</v>
       </c>
       <c r="R19">
-        <v>0.34</v>
+        <v>0.365</v>
       </c>
       <c r="S19" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="T19">
-        <v>0.2112</v>
+        <v>0.2676</v>
       </c>
       <c r="U19">
-        <v>0.2024</v>
+        <v>0.255</v>
       </c>
       <c r="V19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W19">
-        <v>0.2184</v>
+        <v>0.2507</v>
       </c>
       <c r="X19">
-        <v>0.2248</v>
+        <v>0.2216</v>
       </c>
       <c r="Y19">
-        <v>0.9863</v>
+        <v>1.0315</v>
       </c>
       <c r="AA19" t="s">
         <v>44</v>
@@ -2538,22 +2538,22 @@
         <v>44</v>
       </c>
       <c r="AD19">
-        <v>4.37</v>
+        <v>6.82</v>
       </c>
       <c r="AE19" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="AF19">
-        <v>0.2264</v>
+        <v>0.2329</v>
       </c>
       <c r="AG19">
-        <v>0.9391</v>
+        <v>1.2075</v>
       </c>
       <c r="AH19">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="AM19">
-        <v>4.37</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/data/k-props/2026-08-20.xlsx
+++ b/data/k-props/2026-08-20.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="73">
   <si>
     <t>date</t>
   </si>
@@ -208,12 +208,12 @@
     <t>New York Yankees @ Baltimore Orioles</t>
   </si>
   <si>
-    <t>lineup_unweighted_30d_projected_regulars</t>
-  </si>
-  <si>
     <t>Kyle Bradish</t>
   </si>
   <si>
+    <t>6-7</t>
+  </si>
+  <si>
     <t>Andrew Alvarez</t>
   </si>
   <si>
@@ -230,9 +230,6 @@
   </si>
   <si>
     <t>Peter Lambert</t>
-  </si>
-  <si>
-    <t>6-7</t>
   </si>
 </sst>
 </file>
@@ -776,22 +773,22 @@
         <v>6</v>
       </c>
       <c r="M2">
-        <v>0.1691</v>
+        <v>0.1703</v>
       </c>
       <c r="N2">
         <v>5</v>
       </c>
       <c r="O2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="P2">
-        <v>4.08</v>
+        <v>4.06</v>
       </c>
       <c r="Q2">
-        <v>0.1802</v>
+        <v>0.2019</v>
       </c>
       <c r="R2">
-        <v>0.357</v>
+        <v>0.342</v>
       </c>
       <c r="S2" t="s">
         <v>43</v>
@@ -806,10 +803,10 @@
         <v>9</v>
       </c>
       <c r="W2">
-        <v>0.2559</v>
+        <v>0.2555</v>
       </c>
       <c r="X2">
-        <v>0.2216</v>
+        <v>0.2204</v>
       </c>
       <c r="Y2">
         <v>1.0392</v>
@@ -821,22 +818,22 @@
         <v>44</v>
       </c>
       <c r="AD2">
-        <v>5.26</v>
+        <v>5.51</v>
       </c>
       <c r="AE2" t="s">
         <v>45</v>
       </c>
       <c r="AF2">
-        <v>0.1731</v>
+        <v>0.1811</v>
       </c>
       <c r="AG2">
-        <v>1.3047</v>
+        <v>1.3117</v>
       </c>
       <c r="AH2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>5.26</v>
+        <v>5.51</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
@@ -865,7 +862,7 @@
         <v>42</v>
       </c>
       <c r="I3">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="J3" t="b">
         <v>0</v>
@@ -877,7 +874,7 @@
         <v>6</v>
       </c>
       <c r="M3">
-        <v>0.1864</v>
+        <v>0.1835</v>
       </c>
       <c r="N3">
         <v>5</v>
@@ -886,10 +883,10 @@
         <v>129</v>
       </c>
       <c r="P3">
-        <v>4.44</v>
+        <v>4.43</v>
       </c>
       <c r="Q3">
-        <v>0.1705</v>
+        <v>0.1473</v>
       </c>
       <c r="R3">
         <v>0.392</v>
@@ -907,10 +904,10 @@
         <v>9</v>
       </c>
       <c r="W3">
-        <v>0.2143</v>
+        <v>0.2137</v>
       </c>
       <c r="X3">
-        <v>0.2216</v>
+        <v>0.2204</v>
       </c>
       <c r="Y3">
         <v>1.017</v>
@@ -922,22 +919,22 @@
         <v>44</v>
       </c>
       <c r="AD3">
-        <v>3.98</v>
+        <v>3.93</v>
       </c>
       <c r="AE3" t="s">
         <v>45</v>
       </c>
       <c r="AF3">
-        <v>0.1802</v>
+        <v>0.1693</v>
       </c>
       <c r="AG3">
-        <v>0.973</v>
+        <v>0.9782</v>
       </c>
       <c r="AH3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>3.98</v>
+        <v>3.93</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -978,22 +975,22 @@
         <v>6</v>
       </c>
       <c r="M4">
-        <v>0.2336</v>
+        <v>0.2265</v>
       </c>
       <c r="N4">
         <v>5</v>
       </c>
       <c r="O4">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="P4">
-        <v>4.24</v>
+        <v>4.26</v>
       </c>
       <c r="Q4">
-        <v>0.1947</v>
+        <v>0.1453</v>
       </c>
       <c r="R4">
-        <v>0.361</v>
+        <v>0.369</v>
       </c>
       <c r="S4" t="s">
         <v>43</v>
@@ -1008,10 +1005,10 @@
         <v>9</v>
       </c>
       <c r="W4">
-        <v>0.2157</v>
+        <v>0.2149</v>
       </c>
       <c r="X4">
-        <v>0.2216</v>
+        <v>0.2204</v>
       </c>
       <c r="Y4">
         <v>0.8801</v>
@@ -1023,22 +1020,22 @@
         <v>44</v>
       </c>
       <c r="AD4">
-        <v>3.09</v>
+        <v>2.8</v>
       </c>
       <c r="AE4" t="s">
         <v>45</v>
       </c>
       <c r="AF4">
-        <v>0.2195</v>
+        <v>0.1965</v>
       </c>
       <c r="AG4">
-        <v>0.7004</v>
+        <v>0.7042</v>
       </c>
       <c r="AH4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>3.09</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
@@ -1067,7 +1064,7 @@
         <v>42</v>
       </c>
       <c r="I5">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
@@ -1079,22 +1076,22 @@
         <v>5</v>
       </c>
       <c r="M5">
-        <v>0.3183</v>
+        <v>0.3237</v>
       </c>
       <c r="N5">
         <v>5</v>
       </c>
       <c r="O5">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P5">
-        <v>4.01</v>
+        <v>4.02</v>
       </c>
       <c r="Q5">
-        <v>0.4018</v>
+        <v>0.3982</v>
       </c>
       <c r="R5">
-        <v>0.359</v>
+        <v>0.361</v>
       </c>
       <c r="S5" t="s">
         <v>43</v>
@@ -1109,10 +1106,10 @@
         <v>9</v>
       </c>
       <c r="W5">
-        <v>0.2027</v>
+        <v>0.2042</v>
       </c>
       <c r="X5">
-        <v>0.2216</v>
+        <v>0.2204</v>
       </c>
       <c r="Y5">
         <v>0.9792</v>
@@ -1124,22 +1121,22 @@
         <v>44</v>
       </c>
       <c r="AD5">
-        <v>7.67</v>
+        <v>7.76</v>
       </c>
       <c r="AE5" t="s">
         <v>50</v>
       </c>
       <c r="AF5">
-        <v>0.3482</v>
+        <v>0.3506</v>
       </c>
       <c r="AG5">
-        <v>0.9415</v>
+        <v>0.9466</v>
       </c>
       <c r="AH5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>7.67</v>
+        <v>7.76</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1168,7 +1165,7 @@
         <v>42</v>
       </c>
       <c r="I6">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
@@ -1180,22 +1177,22 @@
         <v>6</v>
       </c>
       <c r="M6">
-        <v>0.1705</v>
+        <v>0.1818</v>
       </c>
       <c r="N6">
         <v>5</v>
       </c>
       <c r="O6">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P6">
-        <v>4.46</v>
+        <v>4.35</v>
       </c>
       <c r="Q6">
-        <v>0.1651</v>
+        <v>0.2</v>
       </c>
       <c r="R6">
-        <v>0.353</v>
+        <v>0.355</v>
       </c>
       <c r="S6" t="s">
         <v>43</v>
@@ -1210,10 +1207,10 @@
         <v>9</v>
       </c>
       <c r="W6">
-        <v>0.1876</v>
+        <v>0.1882</v>
       </c>
       <c r="X6">
-        <v>0.2216</v>
+        <v>0.2204</v>
       </c>
       <c r="Y6">
         <v>0.88</v>
@@ -1225,22 +1222,22 @@
         <v>44</v>
       </c>
       <c r="AD6">
-        <v>2.33</v>
+        <v>2.65</v>
       </c>
       <c r="AE6" t="s">
         <v>45</v>
       </c>
       <c r="AF6">
-        <v>0.1686</v>
+        <v>0.1883</v>
       </c>
       <c r="AG6">
-        <v>0.7231</v>
+        <v>0.727</v>
       </c>
       <c r="AH6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>2.33</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
@@ -1281,22 +1278,22 @@
         <v>6</v>
       </c>
       <c r="M7">
-        <v>0.2882</v>
+        <v>0.2922</v>
       </c>
       <c r="N7">
         <v>5</v>
       </c>
       <c r="O7">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="P7">
-        <v>4.14</v>
+        <v>4.15</v>
       </c>
       <c r="Q7">
-        <v>0.2963</v>
+        <v>0.3333</v>
       </c>
       <c r="R7">
-        <v>0.351</v>
+        <v>0.357</v>
       </c>
       <c r="S7" t="s">
         <v>43</v>
@@ -1311,10 +1308,10 @@
         <v>9</v>
       </c>
       <c r="W7">
-        <v>0.2075</v>
+        <v>0.21</v>
       </c>
       <c r="X7">
-        <v>0.2216</v>
+        <v>0.2204</v>
       </c>
       <c r="Y7">
         <v>0.9434</v>
@@ -1326,22 +1323,22 @@
         <v>44</v>
       </c>
       <c r="AD7">
-        <v>4.06</v>
+        <v>4.34</v>
       </c>
       <c r="AE7" t="s">
         <v>45</v>
       </c>
       <c r="AF7">
-        <v>0.2911</v>
+        <v>0.3069</v>
       </c>
       <c r="AG7">
-        <v>0.7648</v>
+        <v>0.7689</v>
       </c>
       <c r="AH7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>4.06</v>
+        <v>4.34</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
@@ -1370,7 +1367,7 @@
         <v>42</v>
       </c>
       <c r="I8">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
@@ -1382,22 +1379,22 @@
         <v>6</v>
       </c>
       <c r="M8">
-        <v>0.2515</v>
+        <v>0.2438</v>
       </c>
       <c r="N8">
         <v>5</v>
       </c>
       <c r="O8">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="P8">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="Q8">
-        <v>0.2479</v>
+        <v>0.2328</v>
       </c>
       <c r="R8">
-        <v>0.369</v>
+        <v>0.367</v>
       </c>
       <c r="S8" t="s">
         <v>43</v>
@@ -1412,10 +1409,10 @@
         <v>9</v>
       </c>
       <c r="W8">
-        <v>0.2127</v>
+        <v>0.2115</v>
       </c>
       <c r="X8">
-        <v>0.2216</v>
+        <v>0.2204</v>
       </c>
       <c r="Y8">
         <v>0.88</v>
@@ -1427,22 +1424,22 @@
         <v>44</v>
       </c>
       <c r="AD8">
-        <v>4.59</v>
+        <v>4.43</v>
       </c>
       <c r="AE8" t="s">
         <v>45</v>
       </c>
       <c r="AF8">
-        <v>0.2501</v>
+        <v>0.2397</v>
       </c>
       <c r="AG8">
-        <v>0.9263</v>
+        <v>0.9312</v>
       </c>
       <c r="AH8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>4.59</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1471,7 +1468,7 @@
         <v>42</v>
       </c>
       <c r="I9">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
@@ -1483,22 +1480,22 @@
         <v>6</v>
       </c>
       <c r="M9">
-        <v>0.142</v>
+        <v>0.148</v>
       </c>
       <c r="N9">
         <v>5</v>
       </c>
       <c r="O9">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="P9">
-        <v>4.22</v>
+        <v>4.29</v>
       </c>
       <c r="Q9">
-        <v>0.1579</v>
+        <v>0.1638</v>
       </c>
       <c r="R9">
-        <v>0.363</v>
+        <v>0.367</v>
       </c>
       <c r="S9" t="s">
         <v>43</v>
@@ -1513,10 +1510,10 @@
         <v>9</v>
       </c>
       <c r="W9">
-        <v>0.2126</v>
+        <v>0.2117</v>
       </c>
       <c r="X9">
-        <v>0.2216</v>
+        <v>0.2204</v>
       </c>
       <c r="Y9">
         <v>1.0024</v>
@@ -1528,22 +1525,22 @@
         <v>44</v>
       </c>
       <c r="AD9">
-        <v>3.04</v>
+        <v>3.12</v>
       </c>
       <c r="AE9" t="s">
         <v>45</v>
       </c>
       <c r="AF9">
-        <v>0.1478</v>
+        <v>0.1538</v>
       </c>
       <c r="AG9">
-        <v>0.911</v>
+        <v>0.9159</v>
       </c>
       <c r="AH9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>3.04</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
@@ -1572,7 +1569,7 @@
         <v>42</v>
       </c>
       <c r="I10">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
@@ -1584,7 +1581,7 @@
         <v>6</v>
       </c>
       <c r="M10">
-        <v>0.1913</v>
+        <v>0.189</v>
       </c>
       <c r="N10">
         <v>5</v>
@@ -1593,10 +1590,10 @@
         <v>107</v>
       </c>
       <c r="P10">
-        <v>4.31</v>
+        <v>4.28</v>
       </c>
       <c r="Q10">
-        <v>0.1776</v>
+        <v>0.1589</v>
       </c>
       <c r="R10">
         <v>0.349</v>
@@ -1614,10 +1611,10 @@
         <v>9</v>
       </c>
       <c r="W10">
-        <v>0.2352</v>
+        <v>0.2356</v>
       </c>
       <c r="X10">
-        <v>0.2216</v>
+        <v>0.2204</v>
       </c>
       <c r="Y10">
         <v>1.0597</v>
@@ -1629,22 +1626,22 @@
         <v>44</v>
       </c>
       <c r="AD10">
-        <v>4.47</v>
+        <v>4.31</v>
       </c>
       <c r="AE10" t="s">
         <v>45</v>
       </c>
       <c r="AF10">
-        <v>0.1865</v>
+        <v>0.1785</v>
       </c>
       <c r="AG10">
-        <v>1.0627</v>
+        <v>1.0684</v>
       </c>
       <c r="AH10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>4.47</v>
+        <v>4.31</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -1685,22 +1682,22 @@
         <v>6</v>
       </c>
       <c r="M11">
-        <v>0.1811</v>
+        <v>0.1841</v>
       </c>
       <c r="N11">
         <v>5</v>
       </c>
       <c r="O11">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="P11">
-        <v>4.46</v>
+        <v>4.44</v>
       </c>
       <c r="Q11">
-        <v>0.1849</v>
+        <v>0.1983</v>
       </c>
       <c r="R11">
-        <v>0.373</v>
+        <v>0.377</v>
       </c>
       <c r="S11" t="s">
         <v>43</v>
@@ -1715,10 +1712,10 @@
         <v>9</v>
       </c>
       <c r="W11">
-        <v>0.2079</v>
+        <v>0.2098</v>
       </c>
       <c r="X11">
-        <v>0.2216</v>
+        <v>0.2204</v>
       </c>
       <c r="Y11">
         <v>0.9771</v>
@@ -1730,22 +1727,22 @@
         <v>44</v>
       </c>
       <c r="AD11">
-        <v>4.59</v>
+        <v>4.81</v>
       </c>
       <c r="AE11" t="s">
         <v>45</v>
       </c>
       <c r="AF11">
-        <v>0.1825</v>
+        <v>0.1895</v>
       </c>
       <c r="AG11">
-        <v>1.1619</v>
+        <v>1.1681</v>
       </c>
       <c r="AH11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>4.59</v>
+        <v>4.81</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
@@ -1774,7 +1771,7 @@
         <v>42</v>
       </c>
       <c r="I12">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="J12" t="b">
         <v>0</v>
@@ -1786,22 +1783,22 @@
         <v>6</v>
       </c>
       <c r="M12">
-        <v>0.2011</v>
+        <v>0.1993</v>
       </c>
       <c r="N12">
         <v>5</v>
       </c>
       <c r="O12">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="P12">
-        <v>4.15</v>
+        <v>4.19</v>
       </c>
       <c r="Q12">
-        <v>0.1441</v>
+        <v>0.1182</v>
       </c>
       <c r="R12">
-        <v>0.357</v>
+        <v>0.355</v>
       </c>
       <c r="S12" t="s">
         <v>43</v>
@@ -1816,10 +1813,10 @@
         <v>9</v>
       </c>
       <c r="W12">
-        <v>0.2143</v>
+        <v>0.2146</v>
       </c>
       <c r="X12">
-        <v>0.2216</v>
+        <v>0.2204</v>
       </c>
       <c r="Y12">
         <v>1.0224</v>
@@ -1831,22 +1828,22 @@
         <v>44</v>
       </c>
       <c r="AD12">
-        <v>4.95</v>
+        <v>4.66</v>
       </c>
       <c r="AE12" t="s">
         <v>45</v>
       </c>
       <c r="AF12">
-        <v>0.1807</v>
+        <v>0.1705</v>
       </c>
       <c r="AG12">
-        <v>1.0861</v>
+        <v>1.0919</v>
       </c>
       <c r="AH12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>4.95</v>
+        <v>4.66</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
@@ -1875,7 +1872,7 @@
         <v>42</v>
       </c>
       <c r="I13">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
@@ -1887,22 +1884,22 @@
         <v>6</v>
       </c>
       <c r="M13">
-        <v>0.2166</v>
+        <v>0.2156</v>
       </c>
       <c r="N13">
         <v>5</v>
       </c>
       <c r="O13">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="P13">
-        <v>4.28</v>
+        <v>4.34</v>
       </c>
       <c r="Q13">
-        <v>0.2212</v>
+        <v>0.2087</v>
       </c>
       <c r="R13">
-        <v>0.361</v>
+        <v>0.365</v>
       </c>
       <c r="S13" t="s">
         <v>43</v>
@@ -1917,10 +1914,10 @@
         <v>9</v>
       </c>
       <c r="W13">
-        <v>0.2416</v>
+        <v>0.2425</v>
       </c>
       <c r="X13">
-        <v>0.2216</v>
+        <v>0.2204</v>
       </c>
       <c r="Y13">
         <v>0.9308</v>
@@ -1932,22 +1929,22 @@
         <v>44</v>
       </c>
       <c r="AD13">
-        <v>4.3</v>
+        <v>4.19</v>
       </c>
       <c r="AE13" t="s">
         <v>45</v>
       </c>
       <c r="AF13">
-        <v>0.2182</v>
+        <v>0.2131</v>
       </c>
       <c r="AG13">
-        <v>0.9437</v>
+        <v>0.9487</v>
       </c>
       <c r="AH13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>4.3</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -2006,13 +2003,13 @@
         <v>0.381</v>
       </c>
       <c r="S14" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="T14">
-        <v>0.252</v>
+        <v>0.2582</v>
       </c>
       <c r="U14">
-        <v>0.2407</v>
+        <v>0.2431</v>
       </c>
       <c r="V14">
         <v>9</v>
@@ -2021,10 +2018,10 @@
         <v>0.2375</v>
       </c>
       <c r="X14">
-        <v>0.2216</v>
+        <v>0.2204</v>
       </c>
       <c r="Y14">
-        <v>1.0328</v>
+        <v>1.0903</v>
       </c>
       <c r="AA14" t="s">
         <v>44</v>
@@ -2033,7 +2030,7 @@
         <v>44</v>
       </c>
       <c r="AD14">
-        <v>7.63</v>
+        <v>8.29</v>
       </c>
       <c r="AE14" t="s">
         <v>50</v>
@@ -2042,13 +2039,13 @@
         <v>0.2759</v>
       </c>
       <c r="AG14">
-        <v>1.1372</v>
+        <v>1.1714</v>
       </c>
       <c r="AH14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>7.63</v>
+        <v>8.29</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -2056,7 +2053,7 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C15">
         <v>5.5</v>
@@ -2107,13 +2104,13 @@
         <v>0.351</v>
       </c>
       <c r="S15" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="T15">
-        <v>0.2724</v>
+        <v>0.2687</v>
       </c>
       <c r="U15">
-        <v>0.2721</v>
+        <v>0.2704</v>
       </c>
       <c r="V15">
         <v>9</v>
@@ -2122,10 +2119,10 @@
         <v>0.2465</v>
       </c>
       <c r="X15">
-        <v>0.2216</v>
+        <v>0.2204</v>
       </c>
       <c r="Y15">
-        <v>1.0137</v>
+        <v>1.0556</v>
       </c>
       <c r="AA15" t="s">
         <v>44</v>
@@ -2134,22 +2131,22 @@
         <v>44</v>
       </c>
       <c r="AD15">
-        <v>5.89</v>
+        <v>6.08</v>
       </c>
       <c r="AE15" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="AF15">
         <v>0.2017</v>
       </c>
       <c r="AG15">
-        <v>1.2292</v>
+        <v>1.2189</v>
       </c>
       <c r="AH15">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="AM15">
-        <v>5.89</v>
+        <v>6.26</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -2208,13 +2205,13 @@
         <v>0.361</v>
       </c>
       <c r="S16" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="T16">
-        <v>0.2349</v>
+        <v>0.2676</v>
       </c>
       <c r="U16">
-        <v>0.2457</v>
+        <v>0.2488</v>
       </c>
       <c r="V16">
         <v>9</v>
@@ -2223,10 +2220,10 @@
         <v>0.2467</v>
       </c>
       <c r="X16">
-        <v>0.2216</v>
+        <v>0.2204</v>
       </c>
       <c r="Y16">
-        <v>1.0156</v>
+        <v>1.0527</v>
       </c>
       <c r="AA16" t="s">
         <v>44</v>
@@ -2235,7 +2232,7 @@
         <v>44</v>
       </c>
       <c r="AD16">
-        <v>4.18</v>
+        <v>4.97</v>
       </c>
       <c r="AE16" t="s">
         <v>45</v>
@@ -2244,13 +2241,13 @@
         <v>0.1902</v>
       </c>
       <c r="AG16">
-        <v>1.0597</v>
+        <v>1.214</v>
       </c>
       <c r="AH16">
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>4.18</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
@@ -2309,13 +2306,13 @@
         <v>0.327</v>
       </c>
       <c r="S17" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="T17">
-        <v>0.2027</v>
+        <v>0.2167</v>
       </c>
       <c r="U17">
-        <v>0.2069</v>
+        <v>0.2142</v>
       </c>
       <c r="V17">
         <v>9</v>
@@ -2324,10 +2321,10 @@
         <v>0.2066</v>
       </c>
       <c r="X17">
-        <v>0.2216</v>
+        <v>0.2204</v>
       </c>
       <c r="Y17">
-        <v>1.0123</v>
+        <v>1.0365</v>
       </c>
       <c r="AA17" t="s">
         <v>44</v>
@@ -2336,22 +2333,22 @@
         <v>44</v>
       </c>
       <c r="AD17">
-        <v>5.67</v>
+        <v>6.24</v>
       </c>
       <c r="AE17" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="AF17">
         <v>0.2829</v>
       </c>
       <c r="AG17">
-        <v>0.9145</v>
+        <v>0.9832</v>
       </c>
       <c r="AH17">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="AM17">
-        <v>5.67</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
@@ -2410,25 +2407,25 @@
         <v>0.34</v>
       </c>
       <c r="S18" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="T18">
-        <v>0.2112</v>
+        <v>0.1965</v>
       </c>
       <c r="U18">
-        <v>0.2024</v>
+        <v>0.1872</v>
       </c>
       <c r="V18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W18">
         <v>0.2184</v>
       </c>
       <c r="X18">
-        <v>0.2216</v>
+        <v>0.2204</v>
       </c>
       <c r="Y18">
-        <v>0.9863</v>
+        <v>0.9281</v>
       </c>
       <c r="AA18" t="s">
         <v>44</v>
@@ -2437,7 +2434,7 @@
         <v>44</v>
       </c>
       <c r="AD18">
-        <v>4.43</v>
+        <v>3.9</v>
       </c>
       <c r="AE18" t="s">
         <v>45</v>
@@ -2446,13 +2443,13 @@
         <v>0.2264</v>
       </c>
       <c r="AG18">
-        <v>0.9527</v>
+        <v>0.8914</v>
       </c>
       <c r="AH18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>4.43</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -2511,13 +2508,13 @@
         <v>0.365</v>
       </c>
       <c r="S19" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="T19">
-        <v>0.2676</v>
+        <v>0.2117</v>
       </c>
       <c r="U19">
-        <v>0.255</v>
+        <v>0.2254</v>
       </c>
       <c r="V19">
         <v>9</v>
@@ -2526,10 +2523,10 @@
         <v>0.2507</v>
       </c>
       <c r="X19">
-        <v>0.2216</v>
+        <v>0.2204</v>
       </c>
       <c r="Y19">
-        <v>1.0315</v>
+        <v>0.99</v>
       </c>
       <c r="AA19" t="s">
         <v>44</v>
@@ -2538,22 +2535,22 @@
         <v>44</v>
       </c>
       <c r="AD19">
-        <v>6.82</v>
+        <v>5.21</v>
       </c>
       <c r="AE19" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="AF19">
         <v>0.2329</v>
       </c>
       <c r="AG19">
-        <v>1.2075</v>
+        <v>0.9603</v>
       </c>
       <c r="AH19">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="AM19">
-        <v>7</v>
+        <v>5.21</v>
       </c>
     </row>
   </sheetData>

--- a/data/k-props/2026-08-20.xlsx
+++ b/data/k-props/2026-08-20.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="77">
   <si>
     <t>date</t>
   </si>
@@ -145,22 +145,34 @@
     <t>lineup_unweighted_30d_posted</t>
   </si>
   <si>
+    <t>U</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>&lt;6</t>
+  </si>
+  <si>
+    <t>Brady Singer</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>&lt;6</t>
-  </si>
-  <si>
-    <t>Brady Singer</t>
-  </si>
-  <si>
     <t>Landen Roupp</t>
   </si>
   <si>
     <t>San Francisco Giants @ Cleveland Guardians</t>
   </si>
   <si>
+    <t>W</t>
+  </si>
+  <si>
     <t>Gavin Williams</t>
+  </si>
+  <si>
+    <t>O</t>
   </si>
   <si>
     <t>&gt;=7</t>
@@ -811,17 +823,23 @@
       <c r="Y2">
         <v>1.0392</v>
       </c>
+      <c r="Z2">
+        <v>4</v>
+      </c>
       <c r="AA2" t="s">
         <v>44</v>
       </c>
+      <c r="AB2">
+        <v>1.01</v>
+      </c>
       <c r="AC2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD2">
         <v>5.51</v>
       </c>
       <c r="AE2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF2">
         <v>0.1811</v>
@@ -831,6 +849,18 @@
       </c>
       <c r="AH2">
         <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>-1.51</v>
+      </c>
+      <c r="AJ2">
+        <v>1.51</v>
+      </c>
+      <c r="AK2">
+        <v>-1.51</v>
+      </c>
+      <c r="AL2">
+        <v>1.51</v>
       </c>
       <c r="AM2">
         <v>5.51</v>
@@ -841,7 +871,7 @@
         <v>39</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C3">
         <v>4.5</v>
@@ -912,17 +942,23 @@
       <c r="Y3">
         <v>1.017</v>
       </c>
+      <c r="Z3">
+        <v>3</v>
+      </c>
       <c r="AA3" t="s">
         <v>44</v>
       </c>
+      <c r="AB3">
+        <v>-0.57</v>
+      </c>
       <c r="AC3" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AD3">
         <v>3.93</v>
       </c>
       <c r="AE3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF3">
         <v>0.1693</v>
@@ -932,6 +968,18 @@
       </c>
       <c r="AH3">
         <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>-0.93</v>
+      </c>
+      <c r="AJ3">
+        <v>0.93</v>
+      </c>
+      <c r="AK3">
+        <v>-0.93</v>
+      </c>
+      <c r="AL3">
+        <v>0.93</v>
       </c>
       <c r="AM3">
         <v>3.93</v>
@@ -942,7 +990,7 @@
         <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C4">
         <v>4.5</v>
@@ -954,7 +1002,7 @@
         <v>-139</v>
       </c>
       <c r="F4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G4">
         <v>824395</v>
@@ -1013,17 +1061,23 @@
       <c r="Y4">
         <v>0.8801</v>
       </c>
+      <c r="Z4">
+        <v>2</v>
+      </c>
       <c r="AA4" t="s">
         <v>44</v>
       </c>
+      <c r="AB4">
+        <v>-1.7</v>
+      </c>
       <c r="AC4" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="AD4">
         <v>2.8</v>
       </c>
       <c r="AE4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF4">
         <v>0.1965</v>
@@ -1033,6 +1087,18 @@
       </c>
       <c r="AH4">
         <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>-0.8</v>
+      </c>
+      <c r="AJ4">
+        <v>0.8</v>
+      </c>
+      <c r="AK4">
+        <v>-0.8</v>
+      </c>
+      <c r="AL4">
+        <v>0.8</v>
       </c>
       <c r="AM4">
         <v>2.8</v>
@@ -1043,7 +1109,7 @@
         <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C5">
         <v>7.5</v>
@@ -1055,7 +1121,7 @@
         <v>-114</v>
       </c>
       <c r="F5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G5">
         <v>824395</v>
@@ -1114,17 +1180,23 @@
       <c r="Y5">
         <v>0.9792</v>
       </c>
+      <c r="Z5">
+        <v>11</v>
+      </c>
       <c r="AA5" t="s">
-        <v>44</v>
+        <v>53</v>
+      </c>
+      <c r="AB5">
+        <v>0.26</v>
       </c>
       <c r="AC5" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AD5">
         <v>7.76</v>
       </c>
       <c r="AE5" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="AF5">
         <v>0.3506</v>
@@ -1134,6 +1206,18 @@
       </c>
       <c r="AH5">
         <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>3.24</v>
+      </c>
+      <c r="AJ5">
+        <v>3.24</v>
+      </c>
+      <c r="AK5">
+        <v>3.24</v>
+      </c>
+      <c r="AL5">
+        <v>3.24</v>
       </c>
       <c r="AM5">
         <v>7.76</v>
@@ -1144,7 +1228,7 @@
         <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C6">
         <v>3.5</v>
@@ -1156,7 +1240,7 @@
         <v>110</v>
       </c>
       <c r="F6" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G6">
         <v>822934</v>
@@ -1215,17 +1299,23 @@
       <c r="Y6">
         <v>0.88</v>
       </c>
+      <c r="Z6">
+        <v>7</v>
+      </c>
       <c r="AA6" t="s">
-        <v>44</v>
+        <v>53</v>
+      </c>
+      <c r="AB6">
+        <v>-0.85</v>
       </c>
       <c r="AC6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD6">
         <v>2.65</v>
       </c>
       <c r="AE6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF6">
         <v>0.1883</v>
@@ -1235,6 +1325,18 @@
       </c>
       <c r="AH6">
         <v>0</v>
+      </c>
+      <c r="AI6">
+        <v>4.35</v>
+      </c>
+      <c r="AJ6">
+        <v>4.35</v>
+      </c>
+      <c r="AK6">
+        <v>4.35</v>
+      </c>
+      <c r="AL6">
+        <v>4.35</v>
       </c>
       <c r="AM6">
         <v>2.65</v>
@@ -1245,7 +1347,7 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C7">
         <v>5.5</v>
@@ -1257,7 +1359,7 @@
         <v>-134</v>
       </c>
       <c r="F7" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G7">
         <v>822934</v>
@@ -1316,17 +1418,23 @@
       <c r="Y7">
         <v>0.9434</v>
       </c>
+      <c r="Z7">
+        <v>8</v>
+      </c>
       <c r="AA7" t="s">
-        <v>44</v>
+        <v>53</v>
+      </c>
+      <c r="AB7">
+        <v>-1.16</v>
       </c>
       <c r="AC7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD7">
         <v>4.34</v>
       </c>
       <c r="AE7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF7">
         <v>0.3069</v>
@@ -1336,6 +1444,18 @@
       </c>
       <c r="AH7">
         <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>3.66</v>
+      </c>
+      <c r="AJ7">
+        <v>3.66</v>
+      </c>
+      <c r="AK7">
+        <v>3.66</v>
+      </c>
+      <c r="AL7">
+        <v>3.66</v>
       </c>
       <c r="AM7">
         <v>4.34</v>
@@ -1346,7 +1466,7 @@
         <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C8">
         <v>4.5</v>
@@ -1358,7 +1478,7 @@
         <v>116</v>
       </c>
       <c r="F8" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G8">
         <v>824074</v>
@@ -1417,17 +1537,23 @@
       <c r="Y8">
         <v>0.88</v>
       </c>
+      <c r="Z8">
+        <v>3</v>
+      </c>
       <c r="AA8" t="s">
         <v>44</v>
       </c>
+      <c r="AB8">
+        <v>-0.07</v>
+      </c>
       <c r="AC8" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AD8">
         <v>4.43</v>
       </c>
       <c r="AE8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF8">
         <v>0.2397</v>
@@ -1437,6 +1563,18 @@
       </c>
       <c r="AH8">
         <v>0</v>
+      </c>
+      <c r="AI8">
+        <v>-1.43</v>
+      </c>
+      <c r="AJ8">
+        <v>1.43</v>
+      </c>
+      <c r="AK8">
+        <v>-1.43</v>
+      </c>
+      <c r="AL8">
+        <v>1.43</v>
       </c>
       <c r="AM8">
         <v>4.43</v>
@@ -1447,7 +1585,7 @@
         <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C9">
         <v>3.5</v>
@@ -1459,7 +1597,7 @@
         <v>-149</v>
       </c>
       <c r="F9" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G9">
         <v>824074</v>
@@ -1518,17 +1656,23 @@
       <c r="Y9">
         <v>1.0024</v>
       </c>
+      <c r="Z9">
+        <v>4</v>
+      </c>
       <c r="AA9" t="s">
-        <v>44</v>
+        <v>53</v>
+      </c>
+      <c r="AB9">
+        <v>-0.38</v>
       </c>
       <c r="AC9" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AD9">
         <v>3.12</v>
       </c>
       <c r="AE9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF9">
         <v>0.1538</v>
@@ -1538,6 +1682,18 @@
       </c>
       <c r="AH9">
         <v>0</v>
+      </c>
+      <c r="AI9">
+        <v>0.88</v>
+      </c>
+      <c r="AJ9">
+        <v>0.88</v>
+      </c>
+      <c r="AK9">
+        <v>0.88</v>
+      </c>
+      <c r="AL9">
+        <v>0.88</v>
       </c>
       <c r="AM9">
         <v>3.12</v>
@@ -1548,7 +1704,7 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C10">
         <v>4.5</v>
@@ -1560,7 +1716,7 @@
         <v>-135</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G10">
         <v>824589</v>
@@ -1619,17 +1775,23 @@
       <c r="Y10">
         <v>1.0597</v>
       </c>
+      <c r="Z10">
+        <v>3</v>
+      </c>
       <c r="AA10" t="s">
         <v>44</v>
       </c>
+      <c r="AB10">
+        <v>-0.19</v>
+      </c>
       <c r="AC10" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AD10">
         <v>4.31</v>
       </c>
       <c r="AE10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF10">
         <v>0.1785</v>
@@ -1639,6 +1801,18 @@
       </c>
       <c r="AH10">
         <v>0</v>
+      </c>
+      <c r="AI10">
+        <v>-1.31</v>
+      </c>
+      <c r="AJ10">
+        <v>1.31</v>
+      </c>
+      <c r="AK10">
+        <v>-1.31</v>
+      </c>
+      <c r="AL10">
+        <v>1.31</v>
       </c>
       <c r="AM10">
         <v>4.31</v>
@@ -1649,7 +1823,7 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C11">
         <v>4.5</v>
@@ -1661,7 +1835,7 @@
         <v>-130</v>
       </c>
       <c r="F11" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G11">
         <v>824589</v>
@@ -1720,17 +1894,23 @@
       <c r="Y11">
         <v>0.9771</v>
       </c>
+      <c r="Z11">
+        <v>6</v>
+      </c>
       <c r="AA11" t="s">
-        <v>44</v>
+        <v>53</v>
+      </c>
+      <c r="AB11">
+        <v>0.31</v>
       </c>
       <c r="AC11" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AD11">
         <v>4.81</v>
       </c>
       <c r="AE11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF11">
         <v>0.1895</v>
@@ -1740,6 +1920,18 @@
       </c>
       <c r="AH11">
         <v>0</v>
+      </c>
+      <c r="AI11">
+        <v>1.19</v>
+      </c>
+      <c r="AJ11">
+        <v>1.19</v>
+      </c>
+      <c r="AK11">
+        <v>1.19</v>
+      </c>
+      <c r="AL11">
+        <v>1.19</v>
       </c>
       <c r="AM11">
         <v>4.81</v>
@@ -1750,7 +1942,7 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C12">
         <v>4.5</v>
@@ -1762,7 +1954,7 @@
         <v>112</v>
       </c>
       <c r="F12" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G12">
         <v>823747</v>
@@ -1821,17 +2013,23 @@
       <c r="Y12">
         <v>1.0224</v>
       </c>
+      <c r="Z12">
+        <v>3</v>
+      </c>
       <c r="AA12" t="s">
         <v>44</v>
       </c>
+      <c r="AB12">
+        <v>0.16</v>
+      </c>
       <c r="AC12" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AD12">
         <v>4.66</v>
       </c>
       <c r="AE12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF12">
         <v>0.1705</v>
@@ -1841,6 +2039,18 @@
       </c>
       <c r="AH12">
         <v>0</v>
+      </c>
+      <c r="AI12">
+        <v>-1.66</v>
+      </c>
+      <c r="AJ12">
+        <v>1.66</v>
+      </c>
+      <c r="AK12">
+        <v>-1.66</v>
+      </c>
+      <c r="AL12">
+        <v>1.66</v>
       </c>
       <c r="AM12">
         <v>4.66</v>
@@ -1851,7 +2061,7 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C13">
         <v>5.5</v>
@@ -1863,7 +2073,7 @@
         <v>-144</v>
       </c>
       <c r="F13" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G13">
         <v>823747</v>
@@ -1922,17 +2132,23 @@
       <c r="Y13">
         <v>0.9308</v>
       </c>
+      <c r="Z13">
+        <v>4</v>
+      </c>
       <c r="AA13" t="s">
         <v>44</v>
       </c>
+      <c r="AB13">
+        <v>-1.31</v>
+      </c>
       <c r="AC13" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="AD13">
         <v>4.19</v>
       </c>
       <c r="AE13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF13">
         <v>0.2131</v>
@@ -1942,6 +2158,18 @@
       </c>
       <c r="AH13">
         <v>0</v>
+      </c>
+      <c r="AI13">
+        <v>-0.19</v>
+      </c>
+      <c r="AJ13">
+        <v>0.19</v>
+      </c>
+      <c r="AK13">
+        <v>-0.19</v>
+      </c>
+      <c r="AL13">
+        <v>0.19</v>
       </c>
       <c r="AM13">
         <v>4.19</v>
@@ -1952,7 +2180,7 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C14">
         <v>6.5</v>
@@ -1964,7 +2192,7 @@
         <v>-102</v>
       </c>
       <c r="F14" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G14">
         <v>824802</v>
@@ -2023,17 +2251,23 @@
       <c r="Y14">
         <v>1.0903</v>
       </c>
+      <c r="Z14">
+        <v>8</v>
+      </c>
       <c r="AA14" t="s">
-        <v>44</v>
+        <v>53</v>
+      </c>
+      <c r="AB14">
+        <v>1.79</v>
       </c>
       <c r="AC14" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="AD14">
         <v>8.29</v>
       </c>
       <c r="AE14" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="AF14">
         <v>0.2759</v>
@@ -2043,6 +2277,18 @@
       </c>
       <c r="AH14">
         <v>0</v>
+      </c>
+      <c r="AI14">
+        <v>-0.29</v>
+      </c>
+      <c r="AJ14">
+        <v>0.29</v>
+      </c>
+      <c r="AK14">
+        <v>-0.29</v>
+      </c>
+      <c r="AL14">
+        <v>0.29</v>
       </c>
       <c r="AM14">
         <v>8.29</v>
@@ -2053,7 +2299,7 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C15">
         <v>5.5</v>
@@ -2065,7 +2311,7 @@
         <v>112</v>
       </c>
       <c r="F15" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G15">
         <v>824802</v>
@@ -2124,17 +2370,23 @@
       <c r="Y15">
         <v>1.0556</v>
       </c>
+      <c r="Z15">
+        <v>5</v>
+      </c>
       <c r="AA15" t="s">
         <v>44</v>
       </c>
+      <c r="AB15">
+        <v>0.76</v>
+      </c>
       <c r="AC15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD15">
         <v>6.08</v>
       </c>
       <c r="AE15" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="AF15">
         <v>0.2017</v>
@@ -2144,6 +2396,18 @@
       </c>
       <c r="AH15">
         <v>0.18</v>
+      </c>
+      <c r="AI15">
+        <v>-1.08</v>
+      </c>
+      <c r="AJ15">
+        <v>1.08</v>
+      </c>
+      <c r="AK15">
+        <v>-1.26</v>
+      </c>
+      <c r="AL15">
+        <v>1.26</v>
       </c>
       <c r="AM15">
         <v>6.26</v>
@@ -2154,7 +2418,7 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C16">
         <v>4.5</v>
@@ -2166,7 +2430,7 @@
         <v>-124</v>
       </c>
       <c r="F16" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G16">
         <v>822861</v>
@@ -2225,17 +2489,23 @@
       <c r="Y16">
         <v>1.0527</v>
       </c>
+      <c r="Z16">
+        <v>5</v>
+      </c>
       <c r="AA16" t="s">
-        <v>44</v>
+        <v>53</v>
+      </c>
+      <c r="AB16">
+        <v>0.47</v>
       </c>
       <c r="AC16" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AD16">
         <v>4.97</v>
       </c>
       <c r="AE16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF16">
         <v>0.1902</v>
@@ -2245,6 +2515,18 @@
       </c>
       <c r="AH16">
         <v>0</v>
+      </c>
+      <c r="AI16">
+        <v>0.03</v>
+      </c>
+      <c r="AJ16">
+        <v>0.03</v>
+      </c>
+      <c r="AK16">
+        <v>0.03</v>
+      </c>
+      <c r="AL16">
+        <v>0.03</v>
       </c>
       <c r="AM16">
         <v>4.97</v>
@@ -2255,7 +2537,7 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C17">
         <v>6.5</v>
@@ -2267,7 +2549,7 @@
         <v>-140</v>
       </c>
       <c r="F17" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G17">
         <v>822861</v>
@@ -2326,17 +2608,23 @@
       <c r="Y17">
         <v>1.0365</v>
       </c>
+      <c r="Z17">
+        <v>10</v>
+      </c>
       <c r="AA17" t="s">
-        <v>44</v>
+        <v>53</v>
+      </c>
+      <c r="AB17">
+        <v>-0.08</v>
       </c>
       <c r="AC17" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AD17">
         <v>6.24</v>
       </c>
       <c r="AE17" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="AF17">
         <v>0.2829</v>
@@ -2346,6 +2634,18 @@
       </c>
       <c r="AH17">
         <v>0.18</v>
+      </c>
+      <c r="AI17">
+        <v>3.76</v>
+      </c>
+      <c r="AJ17">
+        <v>3.76</v>
+      </c>
+      <c r="AK17">
+        <v>3.58</v>
+      </c>
+      <c r="AL17">
+        <v>3.58</v>
       </c>
       <c r="AM17">
         <v>6.42</v>
@@ -2356,7 +2656,7 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C18">
         <v>4.5</v>
@@ -2368,7 +2668,7 @@
         <v>104</v>
       </c>
       <c r="F18" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G18">
         <v>824153</v>
@@ -2427,17 +2727,23 @@
       <c r="Y18">
         <v>0.9281</v>
       </c>
+      <c r="Z18">
+        <v>6</v>
+      </c>
       <c r="AA18" t="s">
-        <v>44</v>
+        <v>53</v>
+      </c>
+      <c r="AB18">
+        <v>-0.6</v>
       </c>
       <c r="AC18" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AD18">
         <v>3.9</v>
       </c>
       <c r="AE18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF18">
         <v>0.2264</v>
@@ -2447,6 +2753,18 @@
       </c>
       <c r="AH18">
         <v>0</v>
+      </c>
+      <c r="AI18">
+        <v>2.1</v>
+      </c>
+      <c r="AJ18">
+        <v>2.1</v>
+      </c>
+      <c r="AK18">
+        <v>2.1</v>
+      </c>
+      <c r="AL18">
+        <v>2.1</v>
       </c>
       <c r="AM18">
         <v>3.9</v>
@@ -2457,7 +2775,7 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C19">
         <v>5.5</v>
@@ -2469,7 +2787,7 @@
         <v>-114</v>
       </c>
       <c r="F19" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G19">
         <v>824153</v>
@@ -2528,17 +2846,23 @@
       <c r="Y19">
         <v>0.99</v>
       </c>
+      <c r="Z19">
+        <v>3</v>
+      </c>
       <c r="AA19" t="s">
         <v>44</v>
       </c>
+      <c r="AB19">
+        <v>-0.29</v>
+      </c>
       <c r="AC19" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AD19">
         <v>5.21</v>
       </c>
       <c r="AE19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF19">
         <v>0.2329</v>
@@ -2548,6 +2872,18 @@
       </c>
       <c r="AH19">
         <v>0</v>
+      </c>
+      <c r="AI19">
+        <v>-2.21</v>
+      </c>
+      <c r="AJ19">
+        <v>2.21</v>
+      </c>
+      <c r="AK19">
+        <v>-2.21</v>
+      </c>
+      <c r="AL19">
+        <v>2.21</v>
       </c>
       <c r="AM19">
         <v>5.21</v>
